--- a/k_6_krank.xlsx
+++ b/k_6_krank.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9095" activeTab="1"/>
+    <workbookView windowWidth="10848" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="kstand" sheetId="1" r:id="rId1"/>
     <sheet name="pai" sheetId="2" r:id="rId2"/>
+    <sheet name="origin" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="13">
   <si>
     <t>WOCHENTAG</t>
   </si>
@@ -47,22 +48,13 @@
     <t>RH</t>
   </si>
   <si>
-    <t>60/295</t>
+    <t>%</t>
   </si>
   <si>
-    <t>51/295</t>
+    <t>Total</t>
   </si>
   <si>
-    <t>45/295</t>
-  </si>
-  <si>
-    <t>30/295</t>
-  </si>
-  <si>
-    <t>9/295</t>
-  </si>
-  <si>
-    <t>91/295</t>
+    <t>Wochentag</t>
   </si>
 </sst>
 </file>
@@ -70,10 +62,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -85,21 +77,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -107,38 +84,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -153,7 +99,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,6 +122,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -189,10 +150,18 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -205,8 +174,16 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,8 +198,23 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,37 +229,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,7 +247,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,13 +265,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,37 +277,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -357,7 +307,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,13 +319,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -387,37 +373,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,22 +423,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -462,30 +449,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -528,6 +491,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -536,16 +528,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -554,132 +546,135 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1200,7 +1195,7 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>91</c:v>
+                  <c:v>96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2722,7 +2717,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:S301"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="10" outlineLevel="1"/>
@@ -2776,7 +2771,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="4:18">
+    <row r="2" spans="1:19">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
@@ -2819,8 +2817,15 @@
       <c r="R2">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="4:10">
+      <c r="S2">
+        <f>SUM(L2:R2)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D3" t="s">
         <v>1</v>
       </c>
@@ -2843,7 +2848,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="4:10">
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D4" t="s">
         <v>1</v>
       </c>
@@ -2866,7 +2874,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="4:10">
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D5" t="s">
         <v>1</v>
       </c>
@@ -2889,7 +2900,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="4:10">
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D6" t="s">
         <v>1</v>
       </c>
@@ -2912,7 +2926,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="4:10">
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D7" t="s">
         <v>1</v>
       </c>
@@ -2935,7 +2952,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="4:10">
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D8" t="s">
         <v>1</v>
       </c>
@@ -2958,7 +2978,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="4:10">
+    <row r="9" spans="1:10">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D9" t="s">
         <v>1</v>
       </c>
@@ -2981,7 +3004,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="4:8">
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D10" t="s">
         <v>1</v>
       </c>
@@ -2998,7 +3024,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="4:8">
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D11" t="s">
         <v>1</v>
       </c>
@@ -3015,7 +3044,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="4:8">
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D12" t="s">
         <v>1</v>
       </c>
@@ -3032,7 +3064,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="4:8">
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
         <v>1</v>
       </c>
@@ -3049,7 +3084,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="4:8">
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D14" t="s">
         <v>1</v>
       </c>
@@ -3066,7 +3104,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="4:8">
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D15" t="s">
         <v>1</v>
       </c>
@@ -3083,7 +3124,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="4:8">
+    <row r="16" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D16" t="s">
         <v>1</v>
       </c>
@@ -3100,7 +3144,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="4:8">
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D17" t="s">
         <v>1</v>
       </c>
@@ -3117,7 +3164,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="4:8">
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D18" t="s">
         <v>1</v>
       </c>
@@ -3134,7 +3184,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="4:8">
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D19" t="s">
         <v>1</v>
       </c>
@@ -3151,7 +3204,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="4:8">
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D20" t="s">
         <v>1</v>
       </c>
@@ -3168,7 +3224,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="4:8">
+    <row r="21" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="D21" t="s">
         <v>1</v>
       </c>
@@ -3185,7 +3244,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="4:8">
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="D22" t="s">
         <v>1</v>
       </c>
@@ -3202,7 +3264,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="4:8">
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D23" t="s">
         <v>1</v>
       </c>
@@ -3219,7 +3284,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="4:8">
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D24" t="s">
         <v>1</v>
       </c>
@@ -3236,7 +3304,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="4:8">
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D25" t="s">
         <v>1</v>
       </c>
@@ -3253,7 +3324,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="4:8">
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D26" t="s">
         <v>1</v>
       </c>
@@ -3270,7 +3344,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="4:8">
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="D27" t="s">
         <v>1</v>
       </c>
@@ -3287,7 +3364,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="4:8">
+    <row r="28" spans="1:8">
+      <c r="A28" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="D28" t="s">
         <v>1</v>
       </c>
@@ -3304,7 +3384,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="4:8">
+    <row r="29" spans="1:8">
+      <c r="A29" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="D29" t="s">
         <v>1</v>
       </c>
@@ -3321,7 +3404,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="4:8">
+    <row r="30" spans="1:8">
+      <c r="A30" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D30" t="s">
         <v>1</v>
       </c>
@@ -3338,7 +3424,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="4:8">
+    <row r="31" spans="1:8">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D31" t="s">
         <v>1</v>
       </c>
@@ -3352,7 +3441,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="4:8">
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D32" t="s">
         <v>1</v>
       </c>
@@ -3366,7 +3458,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="4:8">
+    <row r="33" spans="1:8">
+      <c r="A33" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D33" t="s">
         <v>1</v>
       </c>
@@ -3380,7 +3475,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="4:8">
+    <row r="34" spans="1:8">
+      <c r="A34" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D34" t="s">
         <v>1</v>
       </c>
@@ -3394,7 +3492,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="4:8">
+    <row r="35" spans="1:8">
+      <c r="A35" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="D35" t="s">
         <v>1</v>
       </c>
@@ -3408,7 +3509,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="4:8">
+    <row r="36" spans="1:8">
+      <c r="A36" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D36" t="s">
         <v>1</v>
       </c>
@@ -3422,7 +3526,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="4:8">
+    <row r="37" spans="1:8">
+      <c r="A37" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="D37" t="s">
         <v>1</v>
       </c>
@@ -3436,7 +3543,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="4:8">
+    <row r="38" spans="1:8">
+      <c r="A38" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D38" t="s">
         <v>1</v>
       </c>
@@ -3450,7 +3560,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="4:8">
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D39" t="s">
         <v>1</v>
       </c>
@@ -3464,7 +3577,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="4:8">
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D40" t="s">
         <v>1</v>
       </c>
@@ -3478,7 +3594,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="4:8">
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D41" t="s">
         <v>1</v>
       </c>
@@ -3492,7 +3611,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="4:8">
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D42" t="s">
         <v>1</v>
       </c>
@@ -3506,7 +3628,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="4:8">
+    <row r="43" spans="1:8">
+      <c r="A43" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="D43" t="s">
         <v>1</v>
       </c>
@@ -3520,7 +3645,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="4:8">
+    <row r="44" spans="1:8">
+      <c r="A44" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D44" t="s">
         <v>1</v>
       </c>
@@ -3534,7 +3662,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="4:8">
+    <row r="45" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D45" t="s">
         <v>1</v>
       </c>
@@ -3548,7 +3679,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="4:8">
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D46" t="s">
         <v>1</v>
       </c>
@@ -3559,7 +3693,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="4:8">
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D47" t="s">
         <v>1</v>
       </c>
@@ -3570,7 +3707,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="4:8">
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D48" t="s">
         <v>1</v>
       </c>
@@ -3581,7 +3721,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="4:8">
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D49" t="s">
         <v>1</v>
       </c>
@@ -3592,7 +3735,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="4:8">
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="D50" t="s">
         <v>1</v>
       </c>
@@ -3603,7 +3749,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="4:8">
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D51" t="s">
         <v>1</v>
       </c>
@@ -3614,7 +3763,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="4:8">
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D52" t="s">
         <v>1</v>
       </c>
@@ -3622,7 +3774,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="4:8">
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D53" t="s">
         <v>1</v>
       </c>
@@ -3630,7 +3785,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="4:8">
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D54" t="s">
         <v>1</v>
       </c>
@@ -3638,7 +3796,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="4:8">
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D55" t="s">
         <v>1</v>
       </c>
@@ -3646,7 +3807,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="4:8">
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D56" t="s">
         <v>1</v>
       </c>
@@ -3654,7 +3818,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="4:8">
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D57" t="s">
         <v>1</v>
       </c>
@@ -3662,7 +3829,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="4:8">
+    <row r="58" spans="1:8">
+      <c r="A58" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D58" t="s">
         <v>1</v>
       </c>
@@ -3670,7 +3840,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="4:8">
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D59" t="s">
         <v>1</v>
       </c>
@@ -3678,7 +3851,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="4:8">
+    <row r="60" spans="1:8">
+      <c r="A60" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="D60" t="s">
         <v>1</v>
       </c>
@@ -3686,184 +3862,1317 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="8:8">
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="H61" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="8:8">
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="H62" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="8:8">
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="H63" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="8:8">
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="H64" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="8:8">
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="H65" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="8:8">
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="H66" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="8:8">
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H67" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="8:8">
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="H68" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="8:8">
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H69" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="8:8">
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H70" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="8:8">
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="H71" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="8:8">
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H72" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="8:8">
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="H73" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="8:8">
+    <row r="74" spans="1:8">
+      <c r="A74" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H74" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="8:8">
+    <row r="75" spans="1:8">
+      <c r="A75" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H75" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="8:8">
+    <row r="76" spans="1:8">
+      <c r="A76" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="H76" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="8:8">
+    <row r="77" spans="1:8">
+      <c r="A77" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="H77" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="8:8">
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="H78" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="8:8">
+    <row r="79" spans="1:8">
+      <c r="A79" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H79" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="8:8">
+    <row r="80" spans="1:8">
+      <c r="A80" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="H80" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="8:8">
+    <row r="81" spans="1:8">
+      <c r="A81" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="H81" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="8:8">
+    <row r="82" spans="1:8">
+      <c r="A82" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="H82" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="8:8">
+    <row r="83" spans="1:8">
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="H83" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="8:8">
+    <row r="84" spans="1:8">
+      <c r="A84" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H84" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="8:8">
+    <row r="85" spans="1:8">
+      <c r="A85" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="H85" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="8:8">
+    <row r="86" spans="1:8">
+      <c r="A86" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="H86" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="8:8">
+    <row r="87" spans="1:8">
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="H87" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="8:8">
+    <row r="88" spans="1:8">
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="H88" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="8:8">
+    <row r="89" spans="1:8">
+      <c r="A89" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="H89" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="8:8">
+    <row r="90" spans="1:8">
+      <c r="A90" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="H90" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="8:8">
+    <row r="91" spans="1:8">
+      <c r="A91" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="H91" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="8:8">
+    <row r="92" spans="1:8">
+      <c r="A92" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H92" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="8:8">
+    <row r="93" spans="1:8">
+      <c r="A93" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H93" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="8:8">
+    <row r="94" spans="1:8">
+      <c r="A94" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H94" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="8:8">
+    <row r="95" spans="1:8">
+      <c r="A95" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="H95" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="8:8">
+    <row r="96" spans="1:8">
+      <c r="A96" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="H96" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3879,99 +5188,136 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelCol="3"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="2:4">
+    <row r="1" spans="2:5">
       <c r="B1" t="s">
         <v>8</v>
       </c>
       <c r="D1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <v>60</v>
       </c>
-      <c r="C2"/>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <f>ROUNDUP(60/300,2)</f>
+        <v>0.2</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
         <v>51</v>
       </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <f>ROUNDUP(51/300,3)</f>
+        <v>0.17</v>
+      </c>
+      <c r="E3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4">
         <v>45</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <f>ROUNDUP(45/300,3)</f>
+        <v>0.15</v>
+      </c>
+      <c r="E4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5">
+        <f>ROUNDUP(30/300,2)</f>
+        <v>0.1</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6">
+        <f>ROUNDUP(9/300,3)</f>
+        <v>0.03</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7">
+        <v>0.03</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
+        <v>96</v>
+      </c>
+      <c r="D8">
+        <f>ROUNDUP(96/300,3)</f>
+        <v>0.32</v>
+      </c>
+      <c r="E8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
       <c r="B9">
-        <f>SUM(B2:B8)</f>
-        <v>295</v>
+        <v>300</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3979,4 +5325,1521 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A301"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>